--- a/03-成熟度评估/03-局部评估/05-包装工序成熟度评估表.xlsx
+++ b/03-成熟度评估/03-局部评估/05-包装工序成熟度评估表.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,11 +122,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -150,6 +159,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -533,7 +543,13 @@
           <t>05-包装工序成熟度评估表</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -541,6 +557,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -548,13 +565,15 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>包装是紧固件制造的最后工序，包括分选（检测）、称重、包装、标识和入库。该工序的质量直接影响客户体验和产品交付的准确性。防混料、追溯码管理和客户包装要求符合度是关键控制点。</t>
-        </is>
-      </c>
-    </row>
+          <t>包装是制造的最后工序，包括装配（检测）、称重、包装、标识和入库。该工序的质量直接影响客户体验和产品交付的准确性。防混料、追溯码管理和客户包装要求符合度是关键控制点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -562,10 +581,11 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  *  自动分选机/检测机</t>
+          <t xml:space="preserve">  *  自动装配设备/检测机</t>
         </is>
       </c>
     </row>
@@ -604,6 +624,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -611,6 +632,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -646,6 +668,9 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -653,6 +678,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
@@ -660,6 +686,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
@@ -667,6 +694,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
@@ -674,6 +702,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
@@ -681,6 +710,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
@@ -688,6 +718,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
@@ -695,6 +726,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
@@ -702,6 +734,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
@@ -709,6 +742,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
@@ -716,6 +750,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
@@ -723,6 +758,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
@@ -730,6 +766,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
@@ -737,6 +774,9 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
@@ -744,6 +784,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
@@ -751,6 +792,9 @@
         </is>
       </c>
     </row>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
@@ -758,6 +802,7 @@
         </is>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
@@ -765,6 +810,7 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
@@ -772,6 +818,7 @@
         </is>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -779,6 +826,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
@@ -971,17 +1019,17 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>分选设备能力</t>
+          <t>装配设备能力</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>自动分选/检测设备的配置和能力</t>
+          <t>自动装配/检测设备的配置和能力</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>1分：人工分选；2分：基本设备；3分：自动分选；4分：多功能检测；5分：AI视觉检测</t>
+          <t>1分：人工装配；2分：基本设备；3分：自动装配；4分：多功能检测；5分：AI视觉检测</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
